--- a/artfynd/A 54421-2019 artfynd.xlsx
+++ b/artfynd/A 54421-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123964257</v>
+        <v>123964054</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>78524</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,44 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljugaren, Ljugaren, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481983</v>
+        <v>482016</v>
       </c>
       <c r="R2" t="n">
-        <v>6589086</v>
+        <v>6589089</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hål i grov gran efter jakt på hästmyror.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123964054</v>
+        <v>123964257</v>
       </c>
       <c r="B3" t="n">
-        <v>78524</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,34 +803,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljugaren, Ljugaren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482016</v>
+        <v>481983</v>
       </c>
       <c r="R3" t="n">
-        <v>6589089</v>
+        <v>6589086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hål i grov gran efter jakt på hästmyror.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54421-2019 artfynd.xlsx
+++ b/artfynd/A 54421-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123964054</v>
+        <v>123964257</v>
       </c>
       <c r="B2" t="n">
-        <v>78524</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljugaren, Ljugaren, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482016</v>
+        <v>481983</v>
       </c>
       <c r="R2" t="n">
-        <v>6589089</v>
+        <v>6589086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +770,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hål i grov gran efter jakt på hästmyror.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123964257</v>
+        <v>123964054</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>78524</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,44 +818,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljugaren, Ljugaren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481983</v>
+        <v>482016</v>
       </c>
       <c r="R3" t="n">
-        <v>6589086</v>
+        <v>6589089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hål i grov gran efter jakt på hästmyror.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54421-2019 artfynd.xlsx
+++ b/artfynd/A 54421-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123964257</v>
+        <v>123964054</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,44 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljugaren, Ljugaren, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481983</v>
+        <v>482016</v>
       </c>
       <c r="R2" t="n">
-        <v>6589086</v>
+        <v>6589089</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hål i grov gran efter jakt på hästmyror.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123964054</v>
+        <v>123964257</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,34 +803,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljugaren, Ljugaren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>482016</v>
+        <v>481983</v>
       </c>
       <c r="R3" t="n">
-        <v>6589089</v>
+        <v>6589086</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hål i grov gran efter jakt på hästmyror.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54421-2019 artfynd.xlsx
+++ b/artfynd/A 54421-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,118 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124809250</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ljugarhöjden, Ljugarhöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>481997</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6588950</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54421-2019 artfynd.xlsx
+++ b/artfynd/A 54421-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123964054</v>
+        <v>123964257</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ljugaren, Ljugaren, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>482016</v>
+        <v>481983</v>
       </c>
       <c r="R2" t="n">
-        <v>6589089</v>
+        <v>6589086</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +760,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +770,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hål i grov gran efter jakt på hästmyror.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123964257</v>
+        <v>123964054</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,44 +818,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ljugaren, Ljugaren, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481983</v>
+        <v>482016</v>
       </c>
       <c r="R3" t="n">
-        <v>6589086</v>
+        <v>6589089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hål i grov gran efter jakt på hästmyror.</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54421-2019 artfynd.xlsx
+++ b/artfynd/A 54421-2019 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>124809250</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>91131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
